--- a/stories/arbres/ATOM-SEC.PAR.001-06.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tania arrive au parc avec maman. Maman montre un espace. C'est le bac à sable. Maman dit : tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Tania verse le sable. Il est frais. Elle reste dans l'espace montré. Maman s'assoit sur le banc. L'adulte voit. Tania fait un gâteau. Maman dit : je te vois. Plus tard, elles vont au square. Maman montre un autre espace. C'est le tapis de marelle. Maman dit : tu joues ici. C'est l'espace montré. Tania se souvient. Elle saute dans les cases. Parce que maman la voit, Tania reste. Même leçon, autre lieu. L'adulte voit. Les pieds restent dans l'espace montré.</t>
+          <t>Tania arrive au parc avec maman. Maman montre un espace. C'est le bac à sable. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Tania verse le sable. Il est frais. Elle reste dans l'espace montré. Maman s'assoit sur le banc. L'adulte voit. Tania fait un gâteau. Je te vois. Plus tard, elles vont au square. Maman montre un autre espace. C'est le tapis de marelle. Tu joues ici. C'est l'espace montré. Tania se souvient. Elle saute dans les cases. Parce que maman la voit, Tania reste. Même leçon, autre lieu. L'adulte voit. Les pieds restent dans l'espace montré.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Tania arrive au parc avec maman. Maman montre un espace. C'est le bac à sable.
+maman|Tu joues ici. C'est l'espace montré. Ici, l'adulte voit.
+narrateur|Tania verse le sable. Il est frais. Elle reste dans l'espace montré. Maman s'assoit sur le banc. L'adulte voit. Tania fait un gâteau.
+maman|Je te vois. Plus tard, elles vont au square. Maman montre un autre espace. C'est le tapis de marelle.
+maman|Tu joues ici. C'est l'espace montré.
+narrateur|Tania se souvient. Elle saute dans les cases. Parce que maman la voit, Tania reste. Même leçon, autre lieu. L'adulte voit. Les pieds restent dans l'espace montré.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1491,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Tania joue dehors. Où joue-t-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1664,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Tania est dans l'espace montré. Maman la voit. Au parc, puis au square.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1831,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Tania range le seau. Maman lui tend la main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1998,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2038,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-06.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,11 @@
 narrateur|Tania se souvient. Elle saute dans les cases. Parce que maman la voit, Tania reste. Même leçon, autre lieu. L'adulte voit. Les pieds restent dans l'espace montré.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1498,6 +1508,7 @@
           <t>narrateur|Tania joue dehors. Où joue-t-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1669,6 +1680,11 @@
           <t>narrateur|Tania est dans l'espace montré. Maman la voit. Au parc, puis au square.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1836,6 +1852,7 @@
           <t>narrateur|Tania range le seau. Maman lui tend la main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2003,6 +2020,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2021,7 +2039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2045,6 +2063,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2246,6 +2278,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.PAR.001-06.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tania joue où maman voit</t>
+          <t>Le bateau de Sarah</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un bateau de papier flotte. Sarah joue au bac, puis à la marelle du square. Deux lieux, même règle : l'espace montré, l'adulte voit.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tania arrive au parc avec maman. Maman montre un espace. C'est le bac à sable. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Tania verse le sable. Il est frais. Elle reste dans l'espace montré. Maman s'assoit sur le banc. L'adulte voit. Tania fait un gâteau. Je te vois. Plus tard, elles vont au square. Maman montre un autre espace. C'est le tapis de marelle. Tu joues ici. C'est l'espace montré. Tania se souvient. Elle saute dans les cases. Parce que maman la voit, Tania reste. Même leçon, autre lieu. L'adulte voit. Les pieds restent dans l'espace montré.</t>
+          <t>Un petit bateau de papier flotte dans une flaque. Le papier est blanc et un peu mouillé. La flaque tremble quand le vent passe. Le parc sent l'herbe mouillée. Un banc luit, encore humide. Une plume grise est collée au bois. Tu as vu le bateau, Sarah ? Il flotte, maman. Oui. Tout doucement. Sarah s'accroupit. Le papier est froid sous le doigt. Il est mou. Le papier a bu l'eau. En ce moment, maman montre un espace. C'est le bac à sable. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Sarah verse le sable. Il est frais. Elle reste dans l'espace montré. Maman s'assoit sur le banc. L'adulte voit. Sarah fait un gâteau. Un gâteau, maman. Je te vois. Tu restes dans l'espace montré ? Oui. Bravo. Sarah tasse encore le sable. Le gâteau tient un peu. Plus tard, elles vont au square. Le bateau reste dans la flaque. Le chemin sent l'herbe coupée. Maman montre un autre espace. C'est le tapis de marelle. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Sarah se souvient. Elle saute dans les cases. Parce que maman la voit, Sarah reste. Même leçon, autre lieu. L'adulte voit. Les pieds restent dans l'espace montré. Les cases, maman. Je te vois. Tu as repris la règle. Tu as fait du bon travail. Sarah pose un pied sur le un. Le tapis est un peu rêche. Le deux est un peu délavé.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1324,59 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Tania arrive au parc avec maman. Maman montre un espace. C'est le bac à sable.
-maman|Tu joues ici. C'est l'espace montré. Ici, l'adulte voit.
-narrateur|Tania verse le sable. Il est frais. Elle reste dans l'espace montré. Maman s'assoit sur le banc. L'adulte voit. Tania fait un gâteau.
-maman|Je te vois. Plus tard, elles vont au square. Maman montre un autre espace. C'est le tapis de marelle.
-maman|Tu joues ici. C'est l'espace montré.
-narrateur|Tania se souvient. Elle saute dans les cases. Parce que maman la voit, Tania reste. Même leçon, autre lieu. L'adulte voit. Les pieds restent dans l'espace montré.</t>
+          <t>narrateur|Un petit bateau de papier flotte dans une flaque.
+narrateur|Le papier est blanc et un peu mouillé.
+narrateur|La flaque tremble quand le vent passe.
+narrateur|Le parc sent l'herbe mouillée.
+narrateur|Un banc luit, encore humide.
+narrateur|Une plume grise est collée au bois.
+maman|Tu as vu le bateau, Sarah ?
+enfant-f|Il flotte, maman.
+maman|Oui.
+maman|Tout doucement.
+narrateur|Sarah s'accroupit.
+narrateur|Le papier est froid sous le doigt.
+enfant-f|Il est mou.
+maman|Le papier a bu l'eau.
+narrateur|En ce moment, maman montre un espace.
+narrateur|C'est le bac à sable.
+maman|Tu joues ici.
+maman|C'est l'espace montré.
+maman|Ici, l'adulte voit.
+narrateur|Sarah verse le sable.
+narrateur|Il est frais.
+narrateur|Elle reste dans l'espace montré.
+narrateur|Maman s'assoit sur le banc.
+narrateur|L'adulte voit.
+narrateur|Sarah fait un gâteau.
+enfant-f|Un gâteau, maman.
+maman|Je te vois.
+maman|Tu restes dans l'espace montré ?
+enfant-f|Oui.
+maman|Bravo.
+narrateur|Sarah tasse encore le sable.
+narrateur|Le gâteau tient un peu.
+narrateur|Plus tard, elles vont au square.
+narrateur|Le bateau reste dans la flaque.
+narrateur|Le chemin sent l'herbe coupée.
+narrateur|Maman montre un autre espace.
+narrateur|C'est le tapis de marelle.
+maman|Tu joues ici.
+maman|C'est l'espace montré.
+maman|Ici, l'adulte voit.
+narrateur|Sarah se souvient.
+narrateur|Elle saute dans les cases.
+narrateur|Parce que maman la voit, Sarah reste.
+narrateur|Même leçon, autre lieu.
+narrateur|L'adulte voit.
+narrateur|Les pieds restent dans l'espace montré.
+enfant-f|Les cases, maman.
+maman|Je te vois.
+maman|Tu as repris la règle.
+maman|Tu as fait du bon travail.
+narrateur|Sarah pose un pied sur le un.
+narrateur|Le tapis est un peu rêche.
+narrateur|Le deux est un peu délavé.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1349,7 +1408,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Tania joue dehors. Où joue-t-elle ?</t>
+          <t>Sarah joue dehors. Où joue-t-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1505,10 +1564,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Tania joue dehors. Où joue-t-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Sarah joue dehors.
+narrateur|Où joue-t-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1533,7 +1592,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Tania est dans l'espace montré. Maman la voit. Au parc, puis au square.</t>
+          <t>Sarah est dans l'espace montré. Maman la voit. Au parc, puis au square. L'adulte voit. Tu as joué dans l'espace montré ? Oui. Le bac, puis la marelle. Bravo. Je te voyais. Le gâteau de sable s'est un peu affaissé. Le tapis de marelle est calme.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1677,7 +1736,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Tania est dans l'espace montré. Maman la voit. Au parc, puis au square.</t>
+          <t>narrateur|Sarah est dans l'espace montré.
+narrateur|Maman la voit.
+narrateur|Au parc, puis au square.
+narrateur|L'adulte voit.
+maman|Tu as joué dans l'espace montré ?
+enfant-f|Oui.
+enfant-f|Le bac, puis la marelle.
+maman|Bravo.
+maman|Je te voyais.
+narrateur|Le gâteau de sable s'est un peu affaissé.
+narrateur|Le tapis de marelle est calme.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1709,7 +1778,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Tania range le seau. Maman lui tend la main.</t>
+          <t>Sarah range le seau. Un peu de sable reste sous l'ongle. Maman lui tend la main. Elles repassent près de la flaque. Le bateau est encore là. Oui. Il attend. Toi, tu es restée dans l'espace montré. L'adulte voit. Oui. Bravo, Sarah. Sarah prend la main de maman. Le papier du bateau est tout mou. La plume grise n'est plus sur le banc. Le square sent encore l'herbe.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1849,10 +1918,23 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Tania range le seau. Maman lui tend la main.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Sarah range le seau.
+narrateur|Un peu de sable reste sous l'ongle.
+narrateur|Maman lui tend la main.
+narrateur|Elles repassent près de la flaque.
+enfant-f|Le bateau est encore là.
+maman|Oui.
+maman|Il attend.
+maman|Toi, tu es restée dans l'espace montré.
+enfant-f|L'adulte voit.
+maman|Oui.
+maman|Bravo, Sarah.
+narrateur|Sarah prend la main de maman.
+narrateur|Le papier du bateau est tout mou.
+narrateur|La plume grise n'est plus sur le banc.
+narrateur|Le square sent encore l'herbe.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1877,7 +1959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le petit bateau tourne dans la flaque. J'ai joué au bac. Puis à la marelle. Dans l'espace montré. Bravo, Sarah. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2017,10 +2099,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le petit bateau tourne dans la flaque.
+enfant-f|J'ai joué au bac.
+maman|Puis à la marelle.
+maman|Dans l'espace montré.
+maman|Bravo, Sarah.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2039,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2077,6 +2163,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-06.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-06.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un petit bateau de papier flotte dans une flaque. Le papier est blanc et un peu mouillé. La flaque tremble quand le vent passe. Le parc sent l'herbe mouillée. Un banc luit, encore humide. Une plume grise est collée au bois. Tu as vu le bateau, Sarah ? Il flotte, maman. Oui. Tout doucement. Sarah s'accroupit. Le papier est froid sous le doigt. Il est mou. Le papier a bu l'eau. En ce moment, maman montre un espace. C'est le bac à sable. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Sarah verse le sable. Il est frais. Elle reste dans l'espace montré. Maman s'assoit sur le banc. L'adulte voit. Sarah fait un gâteau. Un gâteau, maman. Je te vois. Tu restes dans l'espace montré ? Oui. Bravo. Sarah tasse encore le sable. Le gâteau tient un peu. Plus tard, elles vont au square. Le bateau reste dans la flaque. Le chemin sent l'herbe coupée. Maman montre un autre espace. C'est le tapis de marelle. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Sarah se souvient. Elle saute dans les cases. Parce que maman la voit, Sarah reste. Même leçon, autre lieu. L'adulte voit. Les pieds restent dans l'espace montré. Les cases, maman. Je te vois. Tu as repris la règle. Tu as fait du bon travail. Sarah pose un pied sur le un. Le tapis est un peu rêche. Le deux est un peu délavé.</t>
+          <t>Un petit bateau de papier flotte dans une flaque. Le papier est blanc et un peu mouillé. La flaque tremble quand le vent passe. Le parc sent l'herbe mouillée. Un banc luit, encore humide. Une plume grise est collée au bois. Tu as vu le bateau, Sarah ? Il flotte, maman. Oui. Tout doucement. Sarah s'accroupit. Le papier est froid sous le doigt. Il est mou. Le papier a bu l'eau. En ce moment, maman montre un espace. C'est le bac à sable. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Sarah verse le sable. Il est frais. Elle reste dans l'espace montré. Maman s'assoit sur le banc. L'adulte voit. Sarah fait un gâteau. Un gâteau, maman. Je te vois. Tu restes dans l'espace montré ? Oui. Bravo. Sarah tasse encore le sable. Le gâteau tient un peu. Plus tard, elles vont au square. Le bateau reste dans la flaque. Le chemin sent l'herbe coupée. Maman montre un autre espace. C'est le tapis de marelle. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Sarah se souvient. Elle saute dans les cases. Parce que maman la voit, Sarah reste. Même leçon, autre lieu. L'adulte voit. Les pieds restent dans l'espace montré. Les cases, maman. Je te vois. Tu as repris la règle. Sarah pose un pied sur le un. Le tapis est un peu rêche. Le deux est un peu délavé.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tania arrive au parc avec maman. Maman montre un &lt;emphasis level="moderate"&gt;espace&lt;/emphasis&gt;. C'est le bac à sable. Maman dit : tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Tania verse le sable. Il est frais. Elle reste dans l'espace montré. Maman s'assoit sur le banc. L'adulte voit. Tania fait un gâteau. Maman dit : je te vois. Plus tard, elles vont au square. Maman montre un autre espace. C'est le tapis de marelle. Maman dit : tu joues ici. C'est l'espace montré. Tania se souvient. Elle saute dans les cases. Parce que maman la voit, Tania reste. Même leçon, autre lieu. L'adulte voit. Les pieds restent dans l'espace montré.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un petit bateau de papier flotte dans une flaque. Le papier est blanc et un peu mouillé. La flaque tremble quand le vent passe. Le parc sent l'herbe mouillée. Un banc luit, encore humide. Une plume grise est collée au bois. Tu as vu le bateau, Sarah ? Il flotte, maman. Oui. Tout doucement. Sarah s'accroupit. Le papier est froid sous le doigt. Il est mou. Le papier a bu l'eau. En ce moment, maman montre un espace. C'est le bac à sable. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Sarah verse le sable. Il est frais. Elle reste dans l'espace montré. Maman s'assoit sur le banc. L'adulte voit. Sarah fait un gâteau. Un gâteau, maman. Je te vois. Tu restes dans l'espace montré ? Oui. Bravo. Sarah tasse encore le sable. Le gâteau tient un peu. Plus tard, elles vont au square. Le bateau reste dans la flaque. Le chemin sent l'herbe coupée. Maman montre un autre espace. C'est le tapis de marelle. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Sarah se souvient. Elle saute dans les cases. Parce que maman la voit, Sarah reste. Même leçon, autre lieu. L'adulte voit. Les pieds restent dans l'espace montré. Les cases, maman. Je te vois. Tu as repris la règle. Sarah pose un pied sur le un. Le tapis est un peu rêche. Le deux est un peu délavé.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1373,7 +1373,6 @@
 enfant-f|Les cases, maman.
 maman|Je te vois.
 maman|Tu as repris la règle.
-maman|Tu as fait du bon travail.
 narrateur|Sarah pose un pied sur le un.
 narrateur|Le tapis est un peu rêche.
 narrateur|Le deux est un peu délavé.</t>
@@ -1413,7 +1412,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tania joue dehors. Où joue-t-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah joue dehors. Où joue-t-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1597,7 +1596,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tania est dans l'&lt;emphasis level="moderate"&gt;espace&lt;/emphasis&gt; montré. Maman la voit. Au parc, puis au square.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah est dans l'espace montré. Maman la voit. Au parc, puis au square. L'adulte voit. Tu as joué dans l'espace montré ? Oui. Le bac, puis la marelle. Bravo. Je te voyais. Le gâteau de sable s'est un peu affaissé. Le tapis de marelle est calme.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1783,7 +1782,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tania range le seau. Maman lui tend la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah range le seau. Un peu de sable reste sous l'ongle. Maman lui tend la main. Elles repassent près de la flaque. Le bateau est encore là. Oui. Il attend. Toi, tu es restée dans l'espace montré. L'adulte voit. Oui. Bravo, Sarah. Sarah prend la main de maman. Le papier du bateau est tout mou. La plume grise n'est plus sur le banc. Le square sent encore l'herbe.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1959,12 +1958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le petit bateau tourne dans la flaque. J'ai joué au bac. Puis à la marelle. Dans l'espace montré. Bravo, Sarah. L'histoire est finie.</t>
+          <t>Le petit bateau tourne dans la flaque. J'ai joué au bac. Puis à la marelle. Dans l'espace montré. Bravo, Sarah.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le petit bateau tourne dans la flaque. J'ai joué au bac. Puis à la marelle. Dans l'espace montré. Bravo, Sarah.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2103,8 +2102,7 @@
 enfant-f|J'ai joué au bac.
 maman|Puis à la marelle.
 maman|Dans l'espace montré.
-maman|Bravo, Sarah.
-narrateur|L'histoire est finie.</t>
+maman|Bravo, Sarah.</t>
         </is>
       </c>
     </row>
@@ -2125,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2170,6 +2168,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-06.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-06.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tania, maman</t>
+          <t>Sarah, maman</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-06.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-06.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le bateau de Sarah</t>
+          <t>Le bateau salé de Sarah</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>parc puis square</t>
+          <t>parc au bord de la mer, tamaris, flaque de sel</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Un bateau de papier flotte. Sarah joue au bac, puis à la marelle du square. Deux lieux, même règle : l'espace montré, l'adulte voit.</t>
+          <t>Sarah veut que son bateau de papier flotte dans la flaque salée. Une coquille brille près de la haie. Maman devient petite. Sarah revient pour le bateau.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un petit bateau de papier flotte dans une flaque. Le papier est blanc et un peu mouillé. La flaque tremble quand le vent passe. Le parc sent l'herbe mouillée. Un banc luit, encore humide. Une plume grise est collée au bois. Tu as vu le bateau, Sarah ? Il flotte, maman. Oui. Tout doucement. Sarah s'accroupit. Le papier est froid sous le doigt. Il est mou. Le papier a bu l'eau. En ce moment, maman montre un espace. C'est le bac à sable. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Sarah verse le sable. Il est frais. Elle reste dans l'espace montré. Maman s'assoit sur le banc. L'adulte voit. Sarah fait un gâteau. Un gâteau, maman. Je te vois. Tu restes dans l'espace montré ? Oui. Bravo. Sarah tasse encore le sable. Le gâteau tient un peu. Plus tard, elles vont au square. Le bateau reste dans la flaque. Le chemin sent l'herbe coupée. Maman montre un autre espace. C'est le tapis de marelle. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Sarah se souvient. Elle saute dans les cases. Parce que maman la voit, Sarah reste. Même leçon, autre lieu. L'adulte voit. Les pieds restent dans l'espace montré. Les cases, maman. Je te vois. Tu as repris la règle. Sarah pose un pied sur le un. Le tapis est un peu rêche. Le deux est un peu délavé.</t>
+          <t>Le vent salé plie les tamaris. Une flaque brille entre les dalles. Elle sent la mer, un peu. Un banc de bois reste encore humide. Une plume grise colle au bois. Tu as vu la flaque, Sarah ? Elle tremble, maman. C'est le vent. Sarah tient un bateau de papier. Le papier est blanc, un peu raide. Je veux qu'il flotte. Dans l'eau salée. On le pose ici, près de moi ? Oui. En ce moment, le papier touche l'eau. L'eau est froide, un peu piquante. Il flotte. Tout doucement. Sarah souffle, tout bas. Le bateau avance d'un souffle. Il part. Je le vois. Je te vois aussi. Une coquille rose luit, très loin. Elle est près de la haie de tamaris. La coquille ! Sarah fait quelques pas vers la haie. Le banc devient petit. Maman devient une petite forme. Le bateau penche dans la flaque, tout seul. Il va se mouiller trop. Sarah revient vers la flaque. Le sel colle déjà sous ses sandales. Tu reviens près du bateau ? Oui. Il est avec toi. Ici, je te vois bien. Le papier a bu un peu d'eau. Il est mou, encore flottant. Il est lourd, maintenant. On le pousse du doigt ? Oui. Le bateau tourne, tout lent. Une goutte de sel brille sur le pouce. Ça pique. C'est la mer, dans la flaque. Le bateau s'arrête contre une dalle. Il est arrivé. Bravo. Il est resté avec nous. Sarah reprend le papier, tout prudent. Il sent le sel et le vent.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Un petit bateau de papier flotte dans une flaque. Le papier est blanc et un peu mouillé. La flaque tremble quand le vent passe. Le parc sent l'herbe mouillée. Un banc luit, encore humide. Une plume grise est collée au bois. Tu as vu le bateau, Sarah ? Il flotte, maman. Oui. Tout doucement. Sarah s'accroupit. Le papier est froid sous le doigt. Il est mou. Le papier a bu l'eau. En ce moment, maman montre un espace. C'est le bac à sable. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Sarah verse le sable. Il est frais. Elle reste dans l'espace montré. Maman s'assoit sur le banc. L'adulte voit. Sarah fait un gâteau. Un gâteau, maman. Je te vois. Tu restes dans l'espace montré ? Oui. Bravo. Sarah tasse encore le sable. Le gâteau tient un peu. Plus tard, elles vont au square. Le bateau reste dans la flaque. Le chemin sent l'herbe coupée. Maman montre un autre espace. C'est le tapis de marelle. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Sarah se souvient. Elle saute dans les cases. Parce que maman la voit, Sarah reste. Même leçon, autre lieu. L'adulte voit. Les pieds restent dans l'espace montré. Les cases, maman. Je te vois. Tu as repris la règle. Sarah pose un pied sur le un. Le tapis est un peu rêche. Le deux est un peu délavé.</t>
+          <t>Le vent salé plie les tamaris. Une flaque brille entre les dalles. Elle sent la mer, un peu. Un banc de bois reste encore humide. Une plume grise colle au bois. Tu as vu la flaque, Sarah ? Elle tremble, maman. C'est le vent. Sarah tient un bateau de papier. Le papier est blanc, un peu raide. Je veux qu'il flotte. Dans l'eau salée. On le pose ici, près de moi ? Oui. En ce moment, le papier touche l'eau. L'eau est froide, un peu piquante. Il flotte. Tout doucement. Sarah souffle, tout bas. Le bateau avance d'un souffle. Il part. Je le vois. Je te vois aussi. Une coquille rose luit, très loin. Elle est près de la haie de tamaris. La coquille ! Sarah fait quelques pas vers la haie. Le banc devient petit. Maman devient une petite forme. Le bateau penche dans la flaque, tout seul. Il va se mouiller trop. Sarah revient vers la flaque. Le sel colle déjà sous ses sandales. Tu reviens près du bateau ? Oui. Il est avec toi. Ici, je te vois bien. Le papier a bu un peu d'eau. Il est mou, encore flottant. Il est lourd, maintenant. On le pousse du doigt ? Oui. Le bateau tourne, tout lent. Une goutte de sel brille sur le pouce. Ça pique. C'est la mer, dans la flaque. Le bateau s'arrête contre une dalle. Il est arrivé. Bravo. Il est resté avec nous. Sarah reprend le papier, tout prudent. Il sent le sel et le vent.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1324,58 +1324,58 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Un petit bateau de papier flotte dans une flaque.
-narrateur|Le papier est blanc et un peu mouillé.
-narrateur|La flaque tremble quand le vent passe.
-narrateur|Le parc sent l'herbe mouillée.
-narrateur|Un banc luit, encore humide.
-narrateur|Une plume grise est collée au bois.
-maman|Tu as vu le bateau, Sarah ?
-enfant-f|Il flotte, maman.
-maman|Oui.
+          <t>narrateur|Le vent salé plie les tamaris.
+narrateur|Une flaque brille entre les dalles.
+narrateur|Elle sent la mer, un peu.
+narrateur|Un banc de bois reste encore humide.
+narrateur|Une plume grise colle au bois.
+maman|Tu as vu la flaque, Sarah ?
+enfant-f|Elle tremble, maman.
+maman|C'est le vent.
+narrateur|Sarah tient un bateau de papier.
+narrateur|Le papier est blanc, un peu raide.
+enfant-f|Je veux qu'il flotte.
+enfant-f|Dans l'eau salée.
+maman|On le pose ici, près de moi ?
+enfant-f|Oui.
+narrateur|En ce moment, le papier touche l'eau.
+narrateur|L'eau est froide, un peu piquante.
+enfant-f|Il flotte.
 maman|Tout doucement.
-narrateur|Sarah s'accroupit.
-narrateur|Le papier est froid sous le doigt.
-enfant-f|Il est mou.
-maman|Le papier a bu l'eau.
-narrateur|En ce moment, maman montre un espace.
-narrateur|C'est le bac à sable.
-maman|Tu joues ici.
-maman|C'est l'espace montré.
-maman|Ici, l'adulte voit.
-narrateur|Sarah verse le sable.
-narrateur|Il est frais.
-narrateur|Elle reste dans l'espace montré.
-narrateur|Maman s'assoit sur le banc.
-narrateur|L'adulte voit.
-narrateur|Sarah fait un gâteau.
-enfant-f|Un gâteau, maman.
-maman|Je te vois.
-maman|Tu restes dans l'espace montré ?
+narrateur|Sarah souffle, tout bas.
+narrateur|Le bateau avance d'un souffle.
+enfant-f|Il part.
+maman|Je le vois.
+maman|Je te vois aussi.
+narrateur|Une coquille rose luit, très loin.
+narrateur|Elle est près de la haie de tamaris.
+enfant-f|La coquille !
+narrateur|Sarah fait quelques pas vers la haie.
+narrateur|Le banc devient petit.
+narrateur|Maman devient une petite forme.
+narrateur|Le bateau penche dans la flaque, tout seul.
+enfant-f|Il va se mouiller trop.
+narrateur|Sarah revient vers la flaque.
+narrateur|Le sel colle déjà sous ses sandales.
+maman|Tu reviens près du bateau ?
 enfant-f|Oui.
+enfant-f|Il est avec toi.
+maman|Ici, je te vois bien.
+narrateur|Le papier a bu un peu d'eau.
+narrateur|Il est mou, encore flottant.
+enfant-f|Il est lourd, maintenant.
+maman|On le pousse du doigt ?
+enfant-f|Oui.
+narrateur|Le bateau tourne, tout lent.
+narrateur|Une goutte de sel brille sur le pouce.
+enfant-f|Ça pique.
+maman|C'est la mer, dans la flaque.
+narrateur|Le bateau s'arrête contre une dalle.
+enfant-f|Il est arrivé.
 maman|Bravo.
-narrateur|Sarah tasse encore le sable.
-narrateur|Le gâteau tient un peu.
-narrateur|Plus tard, elles vont au square.
-narrateur|Le bateau reste dans la flaque.
-narrateur|Le chemin sent l'herbe coupée.
-narrateur|Maman montre un autre espace.
-narrateur|C'est le tapis de marelle.
-maman|Tu joues ici.
-maman|C'est l'espace montré.
-maman|Ici, l'adulte voit.
-narrateur|Sarah se souvient.
-narrateur|Elle saute dans les cases.
-narrateur|Parce que maman la voit, Sarah reste.
-narrateur|Même leçon, autre lieu.
-narrateur|L'adulte voit.
-narrateur|Les pieds restent dans l'espace montré.
-enfant-f|Les cases, maman.
-maman|Je te vois.
-maman|Tu as repris la règle.
-narrateur|Sarah pose un pied sur le un.
-narrateur|Le tapis est un peu rêche.
-narrateur|Le deux est un peu délavé.</t>
+maman|Il est resté avec nous.
+narrateur|Sarah reprend le papier, tout prudent.
+narrateur|Il sent le sel et le vent.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1407,12 +1407,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Sarah joue dehors. Où joue-t-elle ?</t>
+          <t>Sarah joue près du bateau. Où reste-t-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Sarah joue dehors. Où joue-t-elle ?</t>
+          <t>Sarah joue près du bateau. Où reste-t-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>espace montré | ici | le bac | où maman voit | l'espace</t>
+          <t>espace montré | près maman | près de maman | le bateau | où maman voit | ici</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Maman a montré un espace. L'adulte voit. Où joue Tania ?</t>
+          <t>Le bateau est près de maman. Où reste Sarah ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1484,14 +1484,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1563,8 +1563,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Sarah joue dehors.
-narrateur|Où joue-t-elle ?</t>
+          <t>narrateur|Sarah joue près du bateau.
+narrateur|Où reste-t-elle ?</t>
         </is>
       </c>
     </row>
@@ -1591,12 +1591,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah est dans l'espace montré. Maman la voit. Au parc, puis au square. L'adulte voit. Tu as joué dans l'espace montré ? Oui. Le bac, puis la marelle. Bravo. Je te voyais. Le gâteau de sable s'est un peu affaissé. Le tapis de marelle est calme.</t>
+          <t>La coquille rose reste près de la haie. Sarah ne va pas la chercher. Elle tient le papier mouillé. Le bateau était là, avec moi. Oui. Alors je reste. Je te vois, près de la flaque. Elles soufflent encore une fois. Le papier avance, plus lent. Il est fatigué. Il a bu l'eau. Toi, tu es là. Le vent plie encore les tamaris. La plume grise s'envole du banc. Elle part. Le bateau, lui, reste. Sarah pose le papier sur le bois. Le bois est froid, un peu rugueux.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Sarah est dans l'espace montré. Maman la voit. Au parc, puis au square. L'adulte voit. Tu as joué dans l'espace montré ? Oui. Le bac, puis la marelle. Bravo. Je te voyais. Le gâteau de sable s'est un peu affaissé. Le tapis de marelle est calme.</t>
+          <t>La coquille rose reste près de la haie. Sarah ne va pas la chercher. Elle tient le papier mouillé. Le bateau était là, avec moi. Oui. Alors je reste. Je te vois, près de la flaque. Elles soufflent encore une fois. Le papier avance, plus lent. Il est fatigué. Il a bu l'eau. Toi, tu es là. Le vent plie encore les tamaris. La plume grise s'envole du banc. Elle part. Le bateau, lui, reste. Sarah pose le papier sur le bois. Le bois est froid, un peu rugueux.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1659,7 +1659,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1735,17 +1735,24 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sarah est dans l'espace montré.
-narrateur|Maman la voit.
-narrateur|Au parc, puis au square.
-narrateur|L'adulte voit.
-maman|Tu as joué dans l'espace montré ?
+          <t>narrateur|La coquille rose reste près de la haie.
+narrateur|Sarah ne va pas la chercher.
+narrateur|Elle tient le papier mouillé.
+maman|Le bateau était là, avec moi.
 enfant-f|Oui.
-enfant-f|Le bac, puis la marelle.
-maman|Bravo.
-maman|Je te voyais.
-narrateur|Le gâteau de sable s'est un peu affaissé.
-narrateur|Le tapis de marelle est calme.</t>
+enfant-f|Alors je reste.
+maman|Je te vois, près de la flaque.
+narrateur|Elles soufflent encore une fois.
+narrateur|Le papier avance, plus lent.
+enfant-f|Il est fatigué.
+maman|Il a bu l'eau.
+maman|Toi, tu es là.
+narrateur|Le vent plie encore les tamaris.
+narrateur|La plume grise s'envole du banc.
+enfant-f|Elle part.
+maman|Le bateau, lui, reste.
+narrateur|Sarah pose le papier sur le bois.
+narrateur|Le bois est froid, un peu rugueux.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1777,12 +1784,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Sarah range le seau. Un peu de sable reste sous l'ongle. Maman lui tend la main. Elles repassent près de la flaque. Le bateau est encore là. Oui. Il attend. Toi, tu es restée dans l'espace montré. L'adulte voit. Oui. Bravo, Sarah. Sarah prend la main de maman. Le papier du bateau est tout mou. La plume grise n'est plus sur le banc. Le square sent encore l'herbe.</t>
+          <t>Maman tend la gourde. L'eau douce lave le sel de la langue. Tu as soif ? Oui, maman. Le bateau a flotté. Oui. Il était avec nous. Sarah essuie ses doigts sur le linge. Le linge sent le vent. On le pose au soleil ? Pour qu'il sèche. Le papier blanchit un peu, déjà. La flaque tremble encore.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Sarah range le seau. Un peu de sable reste sous l'ongle. Maman lui tend la main. Elles repassent près de la flaque. Le bateau est encore là. Oui. Il attend. Toi, tu es restée dans l'espace montré. L'adulte voit. Oui. Bravo, Sarah. Sarah prend la main de maman. Le papier du bateau est tout mou. La plume grise n'est plus sur le banc. Le square sent encore l'herbe.</t>
+          <t>Maman tend la gourde. L'eau douce lave le sel de la langue. Tu as soif ? Oui, maman. Le bateau a flotté. Oui. Il était avec nous. Sarah essuie ses doigts sur le linge. Le linge sent le vent. On le pose au soleil ? Pour qu'il sèche. Le papier blanchit un peu, déjà. La flaque tremble encore.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1845,7 +1852,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1917,21 +1924,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Sarah range le seau.
-narrateur|Un peu de sable reste sous l'ongle.
-narrateur|Maman lui tend la main.
-narrateur|Elles repassent près de la flaque.
-enfant-f|Le bateau est encore là.
+          <t>narrateur|Maman tend la gourde.
+narrateur|L'eau douce lave le sel de la langue.
+maman|Tu as soif ?
+enfant-f|Oui, maman.
+enfant-f|Le bateau a flotté.
 maman|Oui.
-maman|Il attend.
-maman|Toi, tu es restée dans l'espace montré.
-enfant-f|L'adulte voit.
-maman|Oui.
-maman|Bravo, Sarah.
-narrateur|Sarah prend la main de maman.
-narrateur|Le papier du bateau est tout mou.
-narrateur|La plume grise n'est plus sur le banc.
-narrateur|Le square sent encore l'herbe.</t>
+maman|Il était avec nous.
+narrateur|Sarah essuie ses doigts sur le linge.
+narrateur|Le linge sent le vent.
+maman|On le pose au soleil ?
+enfant-f|Pour qu'il sèche.
+narrateur|Le papier blanchit un peu, déjà.
+narrateur|La flaque tremble encore.</t>
         </is>
       </c>
     </row>
@@ -1958,12 +1963,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le petit bateau tourne dans la flaque. J'ai joué au bac. Puis à la marelle. Dans l'espace montré. Bravo, Sarah.</t>
+          <t>Le bateau sèche sur le banc. Il a flotté. Oui. Le sel colle encore aux doigts. Les tamaris plient, tout doux.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Le petit bateau tourne dans la flaque. J'ai joué au bac. Puis à la marelle. Dans l'espace montré. Bravo, Sarah.</t>
+          <t>Le bateau sèche sur le banc. Il a flotté. Oui. Le sel colle encore aux doigts. Les tamaris plient, tout doux.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2026,7 +2031,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2098,11 +2103,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Le petit bateau tourne dans la flaque.
-enfant-f|J'ai joué au bac.
-maman|Puis à la marelle.
-maman|Dans l'espace montré.
-maman|Bravo, Sarah.</t>
+          <t>narrateur|Le bateau sèche sur le banc.
+enfant-f|Il a flotté.
+maman|Oui.
+narrateur|Le sel colle encore aux doigts.
+narrateur|Les tamaris plient, tout doux.</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2173,6 +2178,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
